--- a/reports/셀린느/history/2026-09-25/셀린느_training_mgf_report.xlsx
+++ b/reports/셀린느/history/2026-09-25/셀린느_training_mgf_report.xlsx
@@ -99,7 +99,7 @@
     <t>1200경 7284조 1008억 2700만</t>
   </si>
   <si>
-    <t>가입 문의:  코빨간돌프/깔지마오  &amp;lt;No.1 레플&amp;gt;</t>
+    <t>가입 문의: 코빨간돌프/깔지마오 &amp;lt;No.1 레플&amp;gt;</t>
   </si>
   <si>
     <t>코빨간돌프</t>
@@ -150,7 +150,7 @@
     <t>1089경 6103조 5933억 8200만</t>
   </si>
   <si>
-    <t>랭킹 98위권이내 용사를 상시 모집중  문의는 설익은체리, 설앵숭, 너굴얌 귓주세요</t>
+    <t>랭킹 98위권이내 용사를 상시 모집중 문의는 설익은체리, 설앵숭, 너굴얌 귓주세요</t>
   </si>
   <si>
     <t>설익은체리</t>
@@ -303,7 +303,7 @@
     <t>129</t>
   </si>
   <si>
-    <t>3465경 3085조 8,290억 7,965만</t>
+    <t>3465경 3085조 8290억 7965만</t>
   </si>
   <si>
     <t>2</t>
@@ -321,7 +321,7 @@
     <t>125</t>
   </si>
   <si>
-    <t>601경 6331조 4,412억 9,078만</t>
+    <t>601경 6331조 4412억 9078만</t>
   </si>
   <si>
     <t>3</t>
@@ -336,7 +336,7 @@
     <t>126</t>
   </si>
   <si>
-    <t>563경 6043조 9,088억 4,883만</t>
+    <t>563경 6043조 9088억 4883만</t>
   </si>
   <si>
     <t>4</t>
@@ -354,7 +354,7 @@
     <t>127</t>
   </si>
   <si>
-    <t>450경 8883조 2,276억 7,901만</t>
+    <t>450경 8883조 2276억 7901만</t>
   </si>
   <si>
     <t>5</t>
@@ -369,7 +369,7 @@
     <t>124</t>
   </si>
   <si>
-    <t>420경 6269조 4,910억 8,038만</t>
+    <t>420경 6269조 4910억 8038만</t>
   </si>
   <si>
     <t>6</t>
@@ -381,7 +381,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BE%B1%ED%99%98</t>
   </si>
   <si>
-    <t>315경 7931조 9,612억 2,036만</t>
+    <t>315경 7931조 9612억 2036만</t>
   </si>
   <si>
     <t>7</t>
@@ -396,7 +396,7 @@
     <t>신궁</t>
   </si>
   <si>
-    <t>284경 2376조 9,293억 7,027만</t>
+    <t>284경 2376조 9293억 7027만</t>
   </si>
   <si>
     <t>8</t>
@@ -414,7 +414,7 @@
     <t>123</t>
   </si>
   <si>
-    <t>135경 6784조 206억 3,874만</t>
+    <t>135경 6784조 206억 3874만</t>
   </si>
   <si>
     <t>9</t>
@@ -426,7 +426,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%ED%88%AC%EA%B8%B0%EB%A6%BF</t>
   </si>
   <si>
-    <t>78경 3119조 9,191억 2,348만</t>
+    <t>78경 3119조 9191억 2348만</t>
   </si>
   <si>
     <t>10</t>
@@ -441,7 +441,7 @@
     <t>122</t>
   </si>
   <si>
-    <t>74경 3470조 8,838억 859만</t>
+    <t>74경 3470조 8838억 859만</t>
   </si>
   <si>
     <t>11</t>
@@ -453,7 +453,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8J</t>
   </si>
   <si>
-    <t>38경 5764조 9,611억 6,669만</t>
+    <t>38경 5764조 9611억 6669만</t>
   </si>
   <si>
     <t>12</t>
@@ -471,7 +471,7 @@
     <t>121</t>
   </si>
   <si>
-    <t>34경 1451조 9,714억 345만</t>
+    <t>34경 1451조 9714억 345만</t>
   </si>
   <si>
     <t>13</t>
@@ -483,7 +483,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EB%A5%B8</t>
   </si>
   <si>
-    <t>30경 7900조 3,282억 3,172만</t>
+    <t>30경 7900조 3282억 3172만</t>
   </si>
   <si>
     <t>14</t>
@@ -498,7 +498,7 @@
     <t>120</t>
   </si>
   <si>
-    <t>22경 6456조 3,137억 8,236만</t>
+    <t>22경 6456조 3137억 8236만</t>
   </si>
   <si>
     <t>15</t>
@@ -513,7 +513,7 @@
     <t>119</t>
   </si>
   <si>
-    <t>19경 3312조 5,233억 2,265만</t>
+    <t>19경 3312조 5233억 2265만</t>
   </si>
   <si>
     <t>16</t>
@@ -525,7 +525,7 @@
     <t>https://mgf.gg/contents/character.php?n=911TurboS</t>
   </si>
   <si>
-    <t>17경 3946조 5,348억 1,517만</t>
+    <t>17경 3946조 5348억 1517만</t>
   </si>
   <si>
     <t>17</t>
@@ -537,7 +537,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%8B%B1</t>
   </si>
   <si>
-    <t>15경 8565조 6,921억 1,543만</t>
+    <t>15경 8565조 6921억 1543만</t>
   </si>
   <si>
     <t>18</t>
@@ -552,7 +552,7 @@
     <t>히어로</t>
   </si>
   <si>
-    <t>10경 9673조 4,839억 2,391만</t>
+    <t>10경 9673조 4839억 2391만</t>
   </si>
   <si>
     <t>19</t>
@@ -570,7 +570,7 @@
     <t>118</t>
   </si>
   <si>
-    <t>10경 9546조 4,143억 8,614만</t>
+    <t>10경 9546조 4143억 8614만</t>
   </si>
   <si>
     <t>20</t>
@@ -582,7 +582,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%9D%BC%EC%9D%B4%ED%8A%B8</t>
   </si>
   <si>
-    <t>8경 6972조 5,711억 9,285만</t>
+    <t>8경 6972조 5711억 9285만</t>
   </si>
   <si>
     <t>21</t>
@@ -594,7 +594,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BF%94%ED%94%BC%EB%A6%AC</t>
   </si>
   <si>
-    <t>6경 4795조 5,878억 5,573만</t>
+    <t>6경 4795조 5878억 5573만</t>
   </si>
   <si>
     <t>22</t>
@@ -609,7 +609,7 @@
     <t>117</t>
   </si>
   <si>
-    <t>6경 4634조 4,428억 4,645만</t>
+    <t>6경 4634조 4428억 4645만</t>
   </si>
   <si>
     <t>23</t>
@@ -621,7 +621,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%8A%AC</t>
   </si>
   <si>
-    <t>6경 4278조 6,791억 8,373만</t>
+    <t>6경 4278조 6791억 8373만</t>
   </si>
   <si>
     <t>24</t>
@@ -633,7 +633,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%ED%83%B1%EA%B5%AC</t>
   </si>
   <si>
-    <t>5경 7426조 2,445억 2,968만</t>
+    <t>5경 7426조 2445억 2968만</t>
   </si>
   <si>
     <t>25</t>
@@ -657,7 +657,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%84%EC%A7%80%EB%A1%9C%EB%84%A4%EC%A6%88</t>
   </si>
   <si>
-    <t>4경 2653조 3,164억 10만</t>
+    <t>4경 2653조 3164억 10만</t>
   </si>
   <si>
     <t>27</t>
@@ -669,7 +669,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%86%94%EB%B9%A0</t>
   </si>
   <si>
-    <t>3경 471조 3,056억 2,823만</t>
+    <t>3경 471조 3056억 2823만</t>
   </si>
   <si>
     <t>28</t>
@@ -681,7 +681,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%94%EC%A7%80%EB%A7%88%EC%98%A4</t>
   </si>
   <si>
-    <t>2경 9330조 6,252억 5,962만</t>
+    <t>2경 9330조 6252억 5962만</t>
   </si>
   <si>
     <t>29</t>
@@ -696,7 +696,7 @@
     <t>115</t>
   </si>
   <si>
-    <t>1경 6272조 175억 1,648만</t>
+    <t>1경 6272조 175억 1648만</t>
   </si>
   <si>
     <t>30</t>
@@ -711,7 +711,7 @@
     <t>116</t>
   </si>
   <si>
-    <t>1경 5136조 8,361억 7,335만</t>
+    <t>1경 5136조 8361억 7335만</t>
   </si>
   <si>
     <t>금은동S2</t>
@@ -720,7 +720,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%88%EC%9D%80%EB%8F%99S2</t>
   </si>
   <si>
-    <t>926경 1868조 5,138억 6,982만</t>
+    <t>926경 1868조 5138억 6982만</t>
   </si>
   <si>
     <t>라온JW</t>
@@ -732,7 +732,7 @@
     <t>아크메이지(불,독)</t>
   </si>
   <si>
-    <t>564경 9054조 2,245억 2,703만</t>
+    <t>564경 9054조 2245억 2703만</t>
   </si>
   <si>
     <t>슨녀</t>
@@ -741,13 +741,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A8%EB%85%80</t>
   </si>
   <si>
-    <t>83경 7316조 4,265억 7,115만</t>
+    <t>83경 7316조 4265억 7115만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%88%EB%9E%84</t>
   </si>
   <si>
-    <t>43경 9111조 4,126억 228만</t>
+    <t>43경 9111조 4126억 228만</t>
   </si>
   <si>
     <t>아마날</t>
@@ -756,7 +756,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A7%88%EB%82%A0</t>
   </si>
   <si>
-    <t>39경 7201조 2,284억 1,187만</t>
+    <t>39경 7201조 2284억 1187만</t>
   </si>
   <si>
     <t>김해님</t>
@@ -765,7 +765,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%95%B4%EB%8B%98</t>
   </si>
   <si>
-    <t>33경 6195조 8,781억 3,849만</t>
+    <t>33경 6195조 8781억 3849만</t>
   </si>
   <si>
     <t>임홀리</t>
@@ -774,7 +774,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%ED%99%80%EB%A6%AC</t>
   </si>
   <si>
-    <t>12경 6271조 4,731억 4,064만</t>
+    <t>12경 6271조 4731억 4064만</t>
   </si>
   <si>
     <t>쁘덍</t>
@@ -783,7 +783,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%81%98%EB%8D%8D</t>
   </si>
   <si>
-    <t>12경 4823조 3,227억 7,538만</t>
+    <t>12경 4823조 3227억 7538만</t>
   </si>
   <si>
     <t>제껴</t>
@@ -792,7 +792,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EA%BB%B4</t>
   </si>
   <si>
-    <t>10경 3952조 5,796억 1,968만</t>
+    <t>10경 3952조 5796억 1968만</t>
   </si>
   <si>
     <t>리브루므</t>
@@ -804,7 +804,7 @@
     <t>보우마스터</t>
   </si>
   <si>
-    <t>7경 5299조 1,666억 2,339만</t>
+    <t>7경 5299조 1666억 2339만</t>
   </si>
   <si>
     <t>엘리자베타</t>
@@ -813,7 +813,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%A6%AC%EC%9E%90%EB%B2%A0%ED%83%80</t>
   </si>
   <si>
-    <t>5경 2625조 4,886억 9,728만</t>
+    <t>5경 2625조 4886억 9728만</t>
   </si>
   <si>
     <t>어흥이다</t>
@@ -822,7 +822,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%B4%ED%9D%A5%EC%9D%B4%EB%8B%A4</t>
   </si>
   <si>
-    <t>5경 2534조 3,569억 771만</t>
+    <t>5경 2534조 3569억 771만</t>
   </si>
   <si>
     <t>우꼬쨩</t>
@@ -831,7 +831,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EA%BC%AC%EC%A8%A9</t>
   </si>
   <si>
-    <t>4경 6715조 9,544억 8,339만</t>
+    <t>4경 6715조 9544억 8339만</t>
   </si>
   <si>
     <t>누룽지룽누</t>
@@ -840,7 +840,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%88%84%EB%A3%BD%EC%A7%80%EB%A3%BD%EB%88%84</t>
   </si>
   <si>
-    <t>4경 6342조 5,950억 7,988만</t>
+    <t>4경 6342조 5950억 7988만</t>
   </si>
   <si>
     <t>비밀키</t>
@@ -849,7 +849,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%B0%80%ED%82%A4</t>
   </si>
   <si>
-    <t>3경 8363조 108억 1,090만</t>
+    <t>3경 8363조 108억 1090만</t>
   </si>
   <si>
     <t>홍시마로</t>
@@ -858,7 +858,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EC%8B%9C%EB%A7%88%EB%A1%9C</t>
   </si>
   <si>
-    <t>3경 3663조 7,765억 3,019만</t>
+    <t>3경 3663조 7765억 3019만</t>
   </si>
   <si>
     <t>붙잡아</t>
@@ -867,7 +867,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%99%EC%9E%A1%EC%95%84</t>
   </si>
   <si>
-    <t>3경 3402조 2,179억 6,058만</t>
+    <t>3경 3402조 2179억 6058만</t>
   </si>
   <si>
     <t>지아라떼</t>
@@ -876,7 +876,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%95%84%EB%9D%BC%EB%96%BC</t>
   </si>
   <si>
-    <t>3경 557조 9,334억 1,681만</t>
+    <t>3경 557조 9334억 1681만</t>
   </si>
   <si>
     <t>슛맨</t>
@@ -885,7 +885,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%9B%EB%A7%A8</t>
   </si>
   <si>
-    <t>2경 8095조 7,314억 2,394만</t>
+    <t>2경 8095조 7314억 2394만</t>
   </si>
   <si>
     <t>o엔젤o</t>
@@ -894,7 +894,7 @@
     <t>https://mgf.gg/contents/character.php?n=o%EC%97%94%EC%A0%A4o</t>
   </si>
   <si>
-    <t>2경 4819조 8,723억 7,152만</t>
+    <t>2경 4819조 8723억 7152만</t>
   </si>
   <si>
     <t>득츈</t>
@@ -903,7 +903,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%93%9D%EC%B8%88</t>
   </si>
   <si>
-    <t>2경 3813조 4,513억 3,727만</t>
+    <t>2경 3813조 4513억 3727만</t>
   </si>
   <si>
     <t>Bit숍</t>
@@ -912,7 +912,7 @@
     <t>https://mgf.gg/contents/character.php?n=Bit%EC%88%8D</t>
   </si>
   <si>
-    <t>2경 2641조 6,242억 7,031만</t>
+    <t>2경 2641조 6242억 7031만</t>
   </si>
   <si>
     <t>메론맛빵</t>
@@ -921,7 +921,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%EB%A1%A0%EB%A7%9B%EB%B9%B5</t>
   </si>
   <si>
-    <t>1경 9736조 4,770억 2,575만</t>
+    <t>1경 9736조 4770억 2575만</t>
   </si>
   <si>
     <t>24년생정춘식</t>
@@ -930,7 +930,7 @@
     <t>https://mgf.gg/contents/character.php?n=24%EB%85%84%EC%83%9D%EC%A0%95%EC%B6%98%EC%8B%9D</t>
   </si>
   <si>
-    <t>1경 7516조 4,862억 2,994만</t>
+    <t>1경 7516조 4862억 2994만</t>
   </si>
   <si>
     <t>시프님</t>
@@ -939,7 +939,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%ED%94%84%EB%8B%98</t>
   </si>
   <si>
-    <t>1경 3725조 4,391억 3,830만</t>
+    <t>1경 3725조 4391억 3830만</t>
   </si>
   <si>
     <t>야옹이다</t>
@@ -948,7 +948,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EC%98%B9%EC%9D%B4%EB%8B%A4</t>
   </si>
   <si>
-    <t>1경 633조 3,863억 8,751만</t>
+    <t>1경 633조 3863억 8751만</t>
   </si>
   <si>
     <t>출장괴물</t>
@@ -957,7 +957,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B6%9C%EC%9E%A5%EA%B4%B4%EB%AC%BC</t>
   </si>
   <si>
-    <t>9636조 9,388억 6,240만</t>
+    <t>9636조 9388억 6240만</t>
   </si>
   <si>
     <t>김똔똔</t>
@@ -966,7 +966,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%98%94%EB%98%94</t>
   </si>
   <si>
-    <t>8547조 7,426억 824만</t>
+    <t>8547조 7426억 824만</t>
   </si>
   <si>
     <t>쏨열무</t>
@@ -975,7 +975,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8F%A8%EC%97%B4%EB%AC%B4</t>
   </si>
   <si>
-    <t>6791조 551억 5,027만</t>
+    <t>6791조 551억 5027만</t>
   </si>
   <si>
     <t>마옥지</t>
@@ -984,7 +984,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%98%A5%EC%A7%80</t>
   </si>
   <si>
-    <t>280경 3220조 6,404억 6,122만</t>
+    <t>280경 3220조 6404억 6122만</t>
   </si>
   <si>
     <t>해물만두야</t>
@@ -993,7 +993,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%AC%BC%EB%A7%8C%EB%91%90%EC%95%BC</t>
   </si>
   <si>
-    <t>231경 7865조 5,718억 420만</t>
+    <t>231경 7865조 5718억 420만</t>
   </si>
   <si>
     <t>캐일리</t>
@@ -1002,7 +1002,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BA%90%EC%9D%BC%EB%A6%AC</t>
   </si>
   <si>
-    <t>186경 7071조 3,782억 8,079만</t>
+    <t>186경 7071조 3782억 8079만</t>
   </si>
   <si>
     <t>설익은앵숭</t>
@@ -1011,7 +1011,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%9D%B5%EC%9D%80%EC%95%B5%EC%88%AD</t>
   </si>
   <si>
-    <t>105경 4731조 5,416억 8,730만</t>
+    <t>105경 4731조 5416억 8730만</t>
   </si>
   <si>
     <t>킹규봉</t>
@@ -1020,7 +1020,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EA%B7%9C%EB%B4%89</t>
   </si>
   <si>
-    <t>85경 8894조 1,952억 8,378만</t>
+    <t>85경 8894조 1952억 8378만</t>
   </si>
   <si>
     <t>설함마</t>
@@ -1029,7 +1029,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%ED%95%A8%EB%A7%88</t>
   </si>
   <si>
-    <t>68경 6411조 7,432억 2,421만</t>
+    <t>68경 6411조 7432억 2421만</t>
   </si>
   <si>
     <t>설묘묘</t>
@@ -1038,7 +1038,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%AC%98%EB%AC%98</t>
   </si>
   <si>
-    <t>46경 1721조 8,958억 6,847만</t>
+    <t>46경 1721조 8958억 6847만</t>
   </si>
   <si>
     <t>루델밍</t>
@@ -1047,7 +1047,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%8D%B8%EB%B0%8D</t>
   </si>
   <si>
-    <t>45경 5109조 8,480억 2,031만</t>
+    <t>45경 5109조 8480억 2031만</t>
   </si>
   <si>
     <t>설봄a</t>
@@ -1059,7 +1059,7 @@
     <t>다크나이트</t>
   </si>
   <si>
-    <t>43경 847조 2,572억 7,170만</t>
+    <t>43경 847조 2572억 7170만</t>
   </si>
   <si>
     <t>너굴얌</t>
@@ -1068,7 +1068,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%84%88%EA%B5%B4%EC%96%8C</t>
   </si>
   <si>
-    <t>42경 3138조 5,889억 4,039만</t>
+    <t>42경 3138조 5889억 4039만</t>
   </si>
   <si>
     <t>시드리안</t>
@@ -1077,7 +1077,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%93%9C%EB%A6%AC%EC%95%88</t>
   </si>
   <si>
-    <t>29경 7613조 5,062억 2,329만</t>
+    <t>29경 7613조 5062억 2329만</t>
   </si>
   <si>
     <t>싲프</t>
@@ -1086,7 +1086,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%B2%ED%94%84</t>
   </si>
   <si>
-    <t>29경 6216조 5,359억 3,679만</t>
+    <t>29경 6216조 5359억 3679만</t>
   </si>
   <si>
     <t>셀렘이</t>
@@ -1095,7 +1095,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%85%80%EB%A0%98%EC%9D%B4</t>
   </si>
   <si>
-    <t>24경 3354조 9,527억 6,259만</t>
+    <t>24경 3354조 9527억 6259만</t>
   </si>
   <si>
     <t>졸귀탱이</t>
@@ -1104,7 +1104,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80%ED%83%B1%EC%9D%B4</t>
   </si>
   <si>
-    <t>20경 5428조 7,775억 656만</t>
+    <t>20경 5428조 7775억 656만</t>
   </si>
   <si>
     <t>설딩</t>
@@ -1113,7 +1113,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%94%A9</t>
   </si>
   <si>
-    <t>19경 7396조 2,622억 1,029만</t>
+    <t>19경 7396조 2622억 1029만</t>
   </si>
   <si>
     <t>마덕칠</t>
@@ -1122,7 +1122,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%8D%95%EC%B9%A0</t>
   </si>
   <si>
-    <t>18경 9870조 503억 9,521만</t>
+    <t>18경 9870조 503억 9521만</t>
   </si>
   <si>
     <t>선콜은차가워</t>
@@ -1131,7 +1131,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EC%BD%9C%EC%9D%80%EC%B0%A8%EA%B0%80%EC%9B%8C</t>
   </si>
   <si>
-    <t>18경 5875조 8,151억 3,649만</t>
+    <t>18경 5875조 8151억 3649만</t>
   </si>
   <si>
     <t>슐아</t>
@@ -1140,7 +1140,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%90%EC%95%84</t>
   </si>
   <si>
-    <t>11경 2907조 6억 1,960만</t>
+    <t>11경 2907조 6억 1960만</t>
   </si>
   <si>
     <t>경성2018</t>
@@ -1149,7 +1149,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%EC%84%B12018</t>
   </si>
   <si>
-    <t>9경 1574조 1,762억 1,736만</t>
+    <t>9경 1574조 1762억 1736만</t>
   </si>
   <si>
     <t>설름</t>
@@ -1167,7 +1167,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%B0%EB%B3%91</t>
   </si>
   <si>
-    <t>6경 5564조 1,888억 7,889만</t>
+    <t>6경 5564조 1888억 7889만</t>
   </si>
   <si>
     <t>다다익숍</t>
@@ -1176,13 +1176,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%88%8D</t>
   </si>
   <si>
-    <t>6경 1783조 4,474억 1,098만</t>
+    <t>6경 1783조 4474억 1098만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%9D%B5%EC%9D%80%EC%B2%B4%EB%A6%AC</t>
   </si>
   <si>
-    <t>5경 5478조 8,492억 3,032만</t>
+    <t>5경 5478조 8492억 3032만</t>
   </si>
   <si>
     <t>애봉얌</t>
@@ -1194,7 +1194,7 @@
     <t>아크메이지(썬,콜)</t>
   </si>
   <si>
-    <t>3경 4312조 1,092억 5,647만</t>
+    <t>3경 4312조 1092억 5647만</t>
   </si>
   <si>
     <t>상구얌</t>
@@ -1203,7 +1203,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EA%B5%AC%EC%96%8C</t>
   </si>
   <si>
-    <t>3경 944조 1,885억 5,352만</t>
+    <t>3경 944조 1885억 5352만</t>
   </si>
   <si>
     <t>설콩순</t>
@@ -1212,7 +1212,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%BD%A9%EC%88%9C</t>
   </si>
   <si>
-    <t>1경 5307조 6,581억 7,894만</t>
+    <t>1경 5307조 6581억 7894만</t>
   </si>
   <si>
     <t>읏코츠</t>
@@ -1221,7 +1221,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%8F%EC%BD%94%EC%B8%A0</t>
   </si>
   <si>
-    <t>1경 5301조 1,854억 5,754만</t>
+    <t>1경 5301조 1854억 5754만</t>
   </si>
   <si>
     <t>설치는정상인</t>
@@ -1230,7 +1230,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%B9%98%EB%8A%94%EC%A0%95%EC%83%81%EC%9D%B8</t>
   </si>
   <si>
-    <t>1경 4592조 3,595억 1,013만</t>
+    <t>1경 4592조 3595억 1013만</t>
   </si>
   <si>
     <t>네오메디</t>
@@ -1239,7 +1239,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EC%98%A4%EB%A9%94%EB%94%94</t>
   </si>
   <si>
-    <t>1경 1050조 7,102억 6,148만</t>
+    <t>1경 1050조 7102억 6148만</t>
   </si>
   <si>
     <t>군보</t>
@@ -1248,7 +1248,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%B0%EB%B3%B4</t>
   </si>
   <si>
-    <t>203경 9556조 9,702억 3,150만</t>
+    <t>203경 9556조 9702억 3150만</t>
   </si>
   <si>
     <t>눙키</t>
@@ -1257,7 +1257,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%88%99%ED%82%A4</t>
   </si>
   <si>
-    <t>128경 6382조 8,779억 8,244만</t>
+    <t>128경 6382조 8779억 8244만</t>
   </si>
   <si>
     <t>5형사</t>
@@ -1266,13 +1266,13 @@
     <t>https://mgf.gg/contents/character.php?n=5%ED%98%95%EC%82%AC</t>
   </si>
   <si>
-    <t>104경 9897조 9,159억 7,613만</t>
+    <t>104경 9897조 9159억 7613만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EC%8A%B52</t>
   </si>
   <si>
-    <t>75경 6411조 4,000억 426만</t>
+    <t>75경 6411조 4000억 426만</t>
   </si>
   <si>
     <t>심천</t>
@@ -1281,7 +1281,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%B2%9C</t>
   </si>
   <si>
-    <t>69경 9303조 5,433억 6,974만</t>
+    <t>69경 9303조 5433억 6974만</t>
   </si>
   <si>
     <t>혁수킹</t>
@@ -1290,7 +1290,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%81%EC%88%98%ED%82%B9</t>
   </si>
   <si>
-    <t>69경 6713조 8,769억 1,358만</t>
+    <t>69경 6713조 8769억 1358만</t>
   </si>
   <si>
     <t>Matter</t>
@@ -1299,7 +1299,7 @@
     <t>https://mgf.gg/contents/character.php?n=Matter</t>
   </si>
   <si>
-    <t>66경 8928조 7,109억 7,340만</t>
+    <t>66경 8928조 7109억 7340만</t>
   </si>
   <si>
     <t>또르뱅</t>
@@ -1308,7 +1308,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EB%A5%B4%EB%B1%85</t>
   </si>
   <si>
-    <t>64경 6281조 8,605억 3,325만</t>
+    <t>64경 6281조 8605억 3325만</t>
   </si>
   <si>
     <t>원중언니</t>
@@ -1317,7 +1317,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%A4%91%EC%96%B8%EB%8B%88</t>
   </si>
   <si>
-    <t>58경 7502조 2,096억 8,571만</t>
+    <t>58경 7502조 2096억 8571만</t>
   </si>
   <si>
     <t>가을호떡</t>
@@ -1326,7 +1326,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%9D%84%ED%98%B8%EB%96%A1</t>
   </si>
   <si>
-    <t>55경 5523조 6,632억 6,782만</t>
+    <t>55경 5523조 6632억 6782만</t>
   </si>
   <si>
     <t>총괄한석현</t>
@@ -1335,7 +1335,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B4%9D%EA%B4%84%ED%95%9C%EC%84%9D%ED%98%84</t>
   </si>
   <si>
-    <t>44경 4442조 9,717억 5,468만</t>
+    <t>44경 4442조 9717억 5468만</t>
   </si>
   <si>
     <t>냠규리</t>
@@ -1344,7 +1344,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%83%A0%EA%B7%9C%EB%A6%AC</t>
   </si>
   <si>
-    <t>39경 129조 8,282억 7,515만</t>
+    <t>39경 129조 8282억 7515만</t>
   </si>
   <si>
     <t>파퍼</t>
@@ -1353,7 +1353,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%ED%8D%BC</t>
   </si>
   <si>
-    <t>32경 7798조 7,344억 3,050만</t>
+    <t>32경 7798조 7344억 3050만</t>
   </si>
   <si>
     <t>김나뭉</t>
@@ -1362,7 +1362,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%82%98%EB%AD%89</t>
   </si>
   <si>
-    <t>30경 8735조 5,003억 7,097만</t>
+    <t>30경 8735조 5003억 7097만</t>
   </si>
   <si>
     <t>Hoood</t>
@@ -1371,7 +1371,7 @@
     <t>https://mgf.gg/contents/character.php?n=Hoood</t>
   </si>
   <si>
-    <t>17경 8032조 1,522억 1,223만</t>
+    <t>17경 8032조 1522억 1223만</t>
   </si>
   <si>
     <t>찐맨듀</t>
@@ -1380,7 +1380,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B0%90%EB%A7%A8%EB%93%80</t>
   </si>
   <si>
-    <t>14경 3225조 9,241억 6,322만</t>
+    <t>14경 3225조 9241억 6322만</t>
   </si>
   <si>
     <t>껌정색</t>
@@ -1389,7 +1389,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BB%8C%EC%A0%95%EC%83%89</t>
   </si>
   <si>
-    <t>14경 1580조 2,176억 6,617만</t>
+    <t>14경 1580조 2176억 6617만</t>
   </si>
   <si>
     <t>다끝남</t>
@@ -1398,7 +1398,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%81%9D%EB%82%A8</t>
   </si>
   <si>
-    <t>13경 5670조 5,033억 9,103만</t>
+    <t>13경 5670조 5033억 9103만</t>
   </si>
   <si>
     <t>이삼2</t>
@@ -1407,7 +1407,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%82%BC2</t>
   </si>
   <si>
-    <t>13경 3744조 5,309억 977만</t>
+    <t>13경 3744조 5309억 977만</t>
   </si>
   <si>
     <t>악경</t>
@@ -1416,7 +1416,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EA%B2%BD</t>
   </si>
   <si>
-    <t>10경 2388조 6,776억 2,691만</t>
+    <t>10경 2388조 6776억 2691만</t>
   </si>
   <si>
     <t>Rahee</t>
@@ -1425,7 +1425,7 @@
     <t>https://mgf.gg/contents/character.php?n=Rahee</t>
   </si>
   <si>
-    <t>7경 8782조 9,990억 6,632만</t>
+    <t>7경 8782조 9990억 6632만</t>
   </si>
   <si>
     <t>고먀츠나나</t>
@@ -1434,7 +1434,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EB%A8%80%EC%B8%A0%EB%82%98%EB%82%98</t>
   </si>
   <si>
-    <t>7경 197조 6,667억 8,901만</t>
+    <t>7경 197조 6667억 8901만</t>
   </si>
   <si>
     <t>딤개</t>
@@ -1443,7 +1443,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%94%A4%EA%B0%9C</t>
   </si>
   <si>
-    <t>5경 8018조 3,068억 3,402만</t>
+    <t>5경 8018조 3068억 3402만</t>
   </si>
   <si>
     <t>히째히째</t>
@@ -1452,7 +1452,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EC%A7%B8%ED%9E%88%EC%A7%B8</t>
   </si>
   <si>
-    <t>4경 6252조 5,336억 736만</t>
+    <t>4경 6252조 5336억 736만</t>
   </si>
   <si>
     <t>통뼈1</t>
@@ -1461,7 +1461,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%86%B5%EB%BC%881</t>
   </si>
   <si>
-    <t>3경 9314조 1,653억 5,009만</t>
+    <t>3경 9314조 1653억 5009만</t>
   </si>
   <si>
     <t>돌로레스</t>
@@ -1470,7 +1470,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EB%A1%9C%EB%A0%88%EC%8A%A4</t>
   </si>
   <si>
-    <t>3경 8262조 6,756억 6,501만</t>
+    <t>3경 8262조 6756억 6501만</t>
   </si>
   <si>
     <t>바람의새벽</t>
@@ -1479,7 +1479,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%94%EB%9E%8C%EC%9D%98%EC%83%88%EB%B2%BD</t>
   </si>
   <si>
-    <t>2경 9221조 4,290억 1,767만</t>
+    <t>2경 9221조 4290억 1767만</t>
   </si>
   <si>
     <t>김도유니</t>
@@ -1488,7 +1488,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8F%84%EC%9C%A0%EB%8B%88</t>
   </si>
   <si>
-    <t>2경 2518조 5,995억 7,371만</t>
+    <t>2경 2518조 5995억 7371만</t>
   </si>
   <si>
     <t>셀러문</t>
@@ -1500,7 +1500,7 @@
     <t>113</t>
   </si>
   <si>
-    <t>4163조 60억 3,041만</t>
+    <t>4163조 60억 3041만</t>
   </si>
   <si>
     <t>라온XR</t>
@@ -1509,7 +1509,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8XR</t>
   </si>
   <si>
-    <t>453경 1832조 9,684억 178만</t>
+    <t>453경 1832조 9684억 178만</t>
   </si>
   <si>
     <t>매스몬스터</t>
@@ -1518,7 +1518,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EC%8A%A4%EB%AA%AC%EC%8A%A4%ED%84%B0</t>
   </si>
   <si>
-    <t>280경 1301조 4,537억 3,951만</t>
+    <t>280경 1301조 4537억 3951만</t>
   </si>
   <si>
     <t>하잉안파파</t>
@@ -1527,7 +1527,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%9E%89%EC%95%88%ED%8C%8C%ED%8C%8C</t>
   </si>
   <si>
-    <t>202경 5067조 3,570억 6,607만</t>
+    <t>202경 5067조 3570억 6607만</t>
   </si>
   <si>
     <t>코코듀</t>
@@ -1536,7 +1536,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EC%BD%94%EB%93%80</t>
   </si>
   <si>
-    <t>106경 8507조 3,404억 2,537만</t>
+    <t>106경 8507조 3404억 2537만</t>
   </si>
   <si>
     <t>타이슨에어랩</t>
@@ -1545,13 +1545,13 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EC%9D%B4%EC%8A%A8%EC%97%90%EC%96%B4%EB%9E%A9</t>
   </si>
   <si>
-    <t>62경 8614조 6,256억 7,372만</t>
+    <t>62경 8614조 6256억 7372만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%ED%81%AC%EB%A9%94%EC%9D%B4%EB%94%A9%EB%8F%99</t>
   </si>
   <si>
-    <t>55경 1587조 5,056억 2,487만</t>
+    <t>55경 1587조 5056억 2487만</t>
   </si>
   <si>
     <t>미야고</t>
@@ -1560,7 +1560,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EC%95%BC%EA%B3%A0</t>
   </si>
   <si>
-    <t>51경 2943조 3,453억 7,104만</t>
+    <t>51경 2943조 3453억 7104만</t>
   </si>
   <si>
     <t>캔드릭</t>
@@ -1569,7 +1569,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BA%94%EB%93%9C%EB%A6%AD</t>
   </si>
   <si>
-    <t>36경 7312조 8,666억 1,977만</t>
+    <t>36경 7312조 8666억 1977만</t>
   </si>
   <si>
     <t>용보이</t>
@@ -1578,7 +1578,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EB%B3%B4%EC%9D%B4</t>
   </si>
   <si>
-    <t>36경 6925조 9,193억 5,914만</t>
+    <t>36경 6925조 9193억 5914만</t>
   </si>
   <si>
     <t>진압조</t>
@@ -1587,7 +1587,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%95%95%EC%A1%B0</t>
   </si>
   <si>
-    <t>23경 5631조 1,681억 611만</t>
+    <t>23경 5631조 1681억 611만</t>
   </si>
   <si>
     <t>똥갈</t>
@@ -1596,7 +1596,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%A5%EA%B0%88</t>
   </si>
   <si>
-    <t>18경 9370조 4,942억 968만</t>
+    <t>18경 9370조 4942억 968만</t>
   </si>
   <si>
     <t>도적왕대현</t>
@@ -1605,7 +1605,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EC%A0%81%EC%99%95%EB%8C%80%ED%98%84</t>
   </si>
   <si>
-    <t>11경 2244조 3,229억 8,341만</t>
+    <t>11경 2244조 3229억 8341만</t>
   </si>
   <si>
     <t>도농롱</t>
@@ -1614,7 +1614,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%86%8D%EB%A1%B1</t>
   </si>
   <si>
-    <t>10경 7295조 4,564억 5,245만</t>
+    <t>10경 7295조 4564억 5245만</t>
   </si>
   <si>
     <t>힐옹</t>
@@ -1623,7 +1623,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%EC%98%B9</t>
   </si>
   <si>
-    <t>8경 8501조 7,368억 9,660만</t>
+    <t>8경 8501조 7368억 9660만</t>
   </si>
   <si>
     <t>반불</t>
@@ -1632,7 +1632,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EB%B6%88</t>
   </si>
   <si>
-    <t>7경 7130조 6,693억 9,364만</t>
+    <t>7경 7130조 6693억 9364만</t>
   </si>
   <si>
     <t>혜도로동</t>
@@ -1641,7 +1641,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EB%8F%84%EB%A1%9C%EB%8F%99</t>
   </si>
   <si>
-    <t>7경 5608조 8,584억 2,657만</t>
+    <t>7경 5608조 8584억 2657만</t>
   </si>
   <si>
     <t>붕어줍</t>
@@ -1650,7 +1650,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%95%EC%96%B4%EC%A4%8D</t>
   </si>
   <si>
-    <t>7경 2005조 2,221억 3,118만</t>
+    <t>7경 2005조 2221억 3118만</t>
   </si>
   <si>
     <t>조명준</t>
@@ -1659,7 +1659,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%AA%85%EC%A4%80</t>
   </si>
   <si>
-    <t>5경 8825조 2,726억 919만</t>
+    <t>5경 8825조 2726억 919만</t>
   </si>
   <si>
     <t>로생</t>
@@ -1668,7 +1668,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EC%83%9D</t>
   </si>
   <si>
-    <t>5경 8284조 8,153억 7,505만</t>
+    <t>5경 8284조 8153억 7505만</t>
   </si>
   <si>
     <t>Redwine</t>
@@ -1686,7 +1686,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%8B%A4%EC%97%B0</t>
   </si>
   <si>
-    <t>5경 4338조 2,243억 5,938만</t>
+    <t>5경 4338조 2243억 5938만</t>
   </si>
   <si>
     <t>망치반죽</t>
@@ -1695,7 +1695,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EB%B0%98%EC%A3%BD</t>
   </si>
   <si>
-    <t>4경 8333조 414억 9,098만</t>
+    <t>4경 8333조 414억 9098만</t>
   </si>
   <si>
     <t>유도로동</t>
@@ -1704,7 +1704,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EB%8F%84%EB%A1%9C%EB%8F%99</t>
   </si>
   <si>
-    <t>4경 3548조 1,193억 5,686만</t>
+    <t>4경 3548조 1193억 5686만</t>
   </si>
   <si>
     <t>그때그아이</t>
@@ -1713,7 +1713,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B7%B8%EB%95%8C%EA%B7%B8%EC%95%84%EC%9D%B4</t>
   </si>
   <si>
-    <t>3경 1551조 4,991억 3,144만</t>
+    <t>3경 1551조 4991억 3144만</t>
   </si>
   <si>
     <t>메키메렁</t>
@@ -1722,7 +1722,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EB%A9%94%EB%A0%81</t>
   </si>
   <si>
-    <t>3경 1254조 3,197억 3,591만</t>
+    <t>3경 1254조 3197억 3591만</t>
   </si>
   <si>
     <t>루빙</t>
@@ -1731,7 +1731,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%B9%99</t>
   </si>
   <si>
-    <t>2경 848조 8,453억 998만</t>
+    <t>2경 848조 8453억 998만</t>
   </si>
   <si>
     <t>꽁꽁얼었다</t>
@@ -1740,7 +1740,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BD%81%EA%BD%81%EC%96%BC%EC%97%88%EB%8B%A4</t>
   </si>
   <si>
-    <t>2경 415조 4,230억 7,944만</t>
+    <t>2경 415조 4230억 7944만</t>
   </si>
   <si>
     <t>spemi</t>
@@ -1749,7 +1749,7 @@
     <t>https://mgf.gg/contents/character.php?n=spemi</t>
   </si>
   <si>
-    <t>1경 8496조 7,102억 7,539만</t>
+    <t>1경 8496조 7102억 7539만</t>
   </si>
   <si>
     <t>우솝이</t>
@@ -1758,7 +1758,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%86%9D%EC%9D%B4</t>
   </si>
   <si>
-    <t>1경 6505조 2,340억 1,882만</t>
+    <t>1경 6505조 2340억 1882만</t>
   </si>
   <si>
     <t>막또날드</t>
@@ -1767,7 +1767,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%89%EB%98%90%EB%82%A0%EB%93%9C</t>
   </si>
   <si>
-    <t>1경 5570조 6,988억 7,323만</t>
+    <t>1경 5570조 6988억 7323만</t>
   </si>
   <si>
     <t>강서구도적</t>
@@ -1776,7 +1776,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EC%84%9C%EA%B5%AC%EB%8F%84%EC%A0%81</t>
   </si>
   <si>
-    <t>561경 8770조 6,553억 4,335만</t>
+    <t>561경 8770조 6553억 4335만</t>
   </si>
   <si>
     <t>따코유</t>
@@ -1785,7 +1785,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%94%B0%EC%BD%94%EC%9C%A0</t>
   </si>
   <si>
-    <t>397경 9870조 1,742억 2,256만</t>
+    <t>397경 9870조 1742억 2256만</t>
   </si>
   <si>
     <t>뚱털</t>
@@ -1794,7 +1794,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9A%B1%ED%84%B8</t>
   </si>
   <si>
-    <t>139경 3957조 7,548억 7,251만</t>
+    <t>139경 3957조 7548억 7251만</t>
   </si>
   <si>
     <t>뽀로로남편</t>
@@ -1803,7 +1803,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%A1%9C%EB%A1%9C%EB%82%A8%ED%8E%B8</t>
   </si>
   <si>
-    <t>109경 3197조 7,992억 7,558만</t>
+    <t>109경 3197조 7992억 7558만</t>
   </si>
   <si>
     <t>귤놈펜</t>
@@ -1812,7 +1812,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B7%A4%EB%86%88%ED%8E%9C</t>
   </si>
   <si>
-    <t>88경 1038조 2,454억 1,638만</t>
+    <t>88경 1038조 2454억 1638만</t>
   </si>
   <si>
     <t>꿀서은</t>
@@ -1821,7 +1821,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BF%80%EC%84%9C%EC%9D%80</t>
   </si>
   <si>
-    <t>34경 695조 9,726억 7,064만</t>
+    <t>34경 695조 9726억 7064만</t>
   </si>
   <si>
     <t>퀸더쪼이</t>
@@ -1830,7 +1830,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%80%B8%EB%8D%94%EC%AA%BC%EC%9D%B4</t>
   </si>
   <si>
-    <t>31경 6241조 1,543억 8,981만</t>
+    <t>31경 6241조 1543억 8981만</t>
   </si>
   <si>
     <t>게탕</t>
@@ -1839,7 +1839,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%8C%ED%83%95</t>
   </si>
   <si>
-    <t>23경 7566조 8,246억 7,693만</t>
+    <t>23경 7566조 8246억 7693만</t>
   </si>
   <si>
     <t>긴나라</t>
@@ -1848,7 +1848,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%B4%EB%82%98%EB%9D%BC</t>
   </si>
   <si>
-    <t>21경 6883조 2,459억 5,189만</t>
+    <t>21경 6883조 2459억 5189만</t>
   </si>
   <si>
     <t>쿨쥐돌</t>
@@ -1857,7 +1857,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BF%A8%EC%A5%90%EB%8F%8C</t>
   </si>
   <si>
-    <t>18경 9649조 7,630억 4,519만</t>
+    <t>18경 9649조 7630억 4519만</t>
   </si>
   <si>
     <t>우둉</t>
@@ -1866,7 +1866,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%91%89</t>
   </si>
   <si>
-    <t>13경 5291조 6,646억 9,579만</t>
+    <t>13경 5291조 6646억 9579만</t>
   </si>
   <si>
     <t>류텐</t>
@@ -1875,7 +1875,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A5%98%ED%85%90</t>
   </si>
   <si>
-    <t>9경 3771조 2,580억 9,733만</t>
+    <t>9경 3771조 2580억 9733만</t>
   </si>
   <si>
     <t>철푸닥</t>
@@ -1884,7 +1884,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%A0%ED%91%B8%EB%8B%A5</t>
   </si>
   <si>
-    <t>7경 7242조 4,697억 2,671만</t>
+    <t>7경 7242조 4697억 2671만</t>
   </si>
   <si>
     <t>원이유이</t>
@@ -1893,7 +1893,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%9D%B4%EC%9C%A0%EC%9D%B4</t>
   </si>
   <si>
-    <t>4경 2472조 8,316억 569만</t>
+    <t>4경 2472조 8316억 569만</t>
   </si>
   <si>
     <t>하드웨어</t>
@@ -1902,7 +1902,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%93%9C%EC%9B%A8%EC%96%B4</t>
   </si>
   <si>
-    <t>3경 7289조 7,623억 1,803만</t>
+    <t>3경 7289조 7623억 1803만</t>
   </si>
   <si>
     <t>ShellyCake</t>
@@ -1911,13 +1911,13 @@
     <t>https://mgf.gg/contents/character.php?n=ShellyCake</t>
   </si>
   <si>
-    <t>2경 8542조 5,263억 2,188만</t>
+    <t>2경 8542조 5263억 2188만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EB%8D%B0%EC%9D%BC2</t>
   </si>
   <si>
-    <t>2경 6547조 7,780억 2,631만</t>
+    <t>2경 6547조 7780억 2631만</t>
   </si>
   <si>
     <t>오정구불독</t>
@@ -1926,7 +1926,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%A0%95%EA%B5%AC%EB%B6%88%EB%8F%85</t>
   </si>
   <si>
-    <t>1경 9840조 8,606억 6,150만</t>
+    <t>1경 9840조 8606억 6150만</t>
   </si>
   <si>
     <t>양덕하늘채</t>
@@ -1935,7 +1935,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EB%8D%95%ED%95%98%EB%8A%98%EC%B1%84</t>
   </si>
   <si>
-    <t>1경 7719조 5,512억 3,060만</t>
+    <t>1경 7719조 5512억 3060만</t>
   </si>
   <si>
     <t>레드플레이어</t>
@@ -1944,7 +1944,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A0%88%EB%93%9C%ED%94%8C%EB%A0%88%EC%9D%B4%EC%96%B4</t>
   </si>
   <si>
-    <t>1경 5246조 8,423억 953만</t>
+    <t>1경 5246조 8423억 953만</t>
   </si>
   <si>
     <t>주하사랑</t>
@@ -1953,7 +1953,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%ED%95%98%EC%82%AC%EB%9E%91</t>
   </si>
   <si>
-    <t>1경 4364조 8,262억 2,018만</t>
+    <t>1경 4364조 8262억 2018만</t>
   </si>
   <si>
     <t>구미적</t>
@@ -1962,7 +1962,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%AF%B8%EC%A0%81</t>
   </si>
   <si>
-    <t>1경 3726조 7,395억 147만</t>
+    <t>1경 3726조 7395억 147만</t>
   </si>
   <si>
     <t>예슬a</t>
@@ -1974,7 +1974,7 @@
     <t>114</t>
   </si>
   <si>
-    <t>1경 2932조 2,761억 2,173만</t>
+    <t>1경 2932조 2761억 2173만</t>
   </si>
   <si>
     <t>검샷</t>
@@ -1983,7 +1983,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%80%EC%83%B7</t>
   </si>
   <si>
-    <t>1경 1615조 5,659억 493만</t>
+    <t>1경 1615조 5659억 493만</t>
   </si>
   <si>
     <t>브리또강철중</t>
@@ -1992,7 +1992,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EB%A6%AC%EB%98%90%EA%B0%95%EC%B2%A0%EC%A4%91</t>
   </si>
   <si>
-    <t>1경 83조 3,899억 404만</t>
+    <t>1경 83조 3899억 404만</t>
   </si>
   <si>
     <t>꼬기갓</t>
@@ -2001,7 +2001,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EA%B8%B0%EA%B0%93</t>
   </si>
   <si>
-    <t>8285조 5,244억 911만</t>
+    <t>8285조 5244억 911만</t>
   </si>
   <si>
     <t>장아린</t>
@@ -2010,7 +2010,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EC%95%84%EB%A6%B0</t>
   </si>
   <si>
-    <t>8133조 6,906억 9,372만</t>
+    <t>8133조 6906억 9372만</t>
   </si>
   <si>
     <t>l빠다코코낫l</t>
@@ -2019,7 +2019,7 @@
     <t>https://mgf.gg/contents/character.php?n=l%EB%B9%A0%EB%8B%A4%EC%BD%94%EC%BD%94%EB%82%ABl</t>
   </si>
   <si>
-    <t>7066조 4,815억 2,818만</t>
+    <t>7066조 4815억 2818만</t>
   </si>
   <si>
     <t>리광춘</t>
@@ -2028,7 +2028,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A6%AC%EA%B4%91%EC%B6%98</t>
   </si>
   <si>
-    <t>6098조 5,009억 8,907만</t>
+    <t>6098조 5009억 8907만</t>
   </si>
   <si>
     <t>어꼬</t>
@@ -2040,7 +2040,7 @@
     <t>112</t>
   </si>
   <si>
-    <t>3751조 3,186억 2,243만</t>
+    <t>3751조 3186억 2243만</t>
   </si>
   <si>
     <t>말레이히어로</t>
@@ -2049,7 +2049,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
   </si>
   <si>
-    <t>25경 4823조 3,360억 295만</t>
+    <t>25경 4823조 3360억 295만</t>
   </si>
   <si>
     <t>부엉이형</t>
@@ -2058,7 +2058,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%ED%98%95</t>
   </si>
   <si>
-    <t>19경 8464조 5,082억 5,270만</t>
+    <t>19경 8464조 5082억 5270만</t>
   </si>
   <si>
     <t>걸음</t>
@@ -2067,7 +2067,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EC%9D%8C</t>
   </si>
   <si>
-    <t>12경 4306조 3,052억 4,003만</t>
+    <t>12경 4306조 3052억 4003만</t>
   </si>
   <si>
     <t>국의</t>
@@ -2076,7 +2076,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EC%9D%98</t>
   </si>
   <si>
-    <t>11경 4105조 7,960억 279만</t>
+    <t>11경 4105조 7960억 279만</t>
+  </si>
+  <si>
+    <t>하후돈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
+  </si>
+  <si>
+    <t>10경 6154조 8799억 4676만</t>
   </si>
   <si>
     <t>약어</t>
@@ -2085,16 +2094,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
   </si>
   <si>
-    <t>10경 4738조 815억 6,221만</t>
-  </si>
-  <si>
-    <t>하후돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
-  </si>
-  <si>
-    <t>10경 3451조 2,235억 7,402만</t>
+    <t>10경 4738조 815억 6221만</t>
   </si>
   <si>
     <t>잼포즈</t>
@@ -2103,7 +2103,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
   </si>
   <si>
-    <t>9경 3290조 8,758억 715만</t>
+    <t>9경 3423조 3510억 8891만</t>
   </si>
   <si>
     <t>꽃을든남자</t>
@@ -2112,7 +2112,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
   </si>
   <si>
-    <t>7경 6148조 2,651억 9,696만</t>
+    <t>7경 6148조 2651억 9696만</t>
+  </si>
+  <si>
+    <t>킹몬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
+  </si>
+  <si>
+    <t>7경 3381조 2238억 1561만</t>
   </si>
   <si>
     <t>니달리신</t>
@@ -2121,16 +2130,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
   </si>
   <si>
-    <t>7경 3059조 933억 2,511만</t>
-  </si>
-  <si>
-    <t>킹몬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
-  </si>
-  <si>
-    <t>6경 7083조 325억 1,634만</t>
+    <t>7경 3059조 933억 2511만</t>
   </si>
   <si>
     <t>쾌감</t>
@@ -2139,7 +2139,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
   </si>
   <si>
-    <t>5경 5228조 9,003억 4,099만</t>
+    <t>5경 5228조 9003억 4099만</t>
   </si>
   <si>
     <t>핫잇</t>
@@ -2148,7 +2148,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%87</t>
   </si>
   <si>
-    <t>2경 4504조 4,834억 827만</t>
+    <t>2경 4504조 4834억 827만</t>
   </si>
   <si>
     <t>할룽</t>
@@ -2157,7 +2157,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
   </si>
   <si>
-    <t>2경 4130조 5,641억 7,043만</t>
+    <t>2경 4130조 5641억 7043만</t>
   </si>
   <si>
     <t>세아수호지호</t>
@@ -2166,7 +2166,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%95%84%EC%88%98%ED%98%B8%EC%A7%80%ED%98%B8</t>
   </si>
   <si>
-    <t>2경 3271조 2,021억 502만</t>
+    <t>2경 3271조 2021억 502만</t>
   </si>
   <si>
     <t>오픈톡쌀숭E</t>
@@ -2175,7 +2175,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%ED%94%88%ED%86%A1%EC%8C%80%EC%88%ADE</t>
   </si>
   <si>
-    <t>2경 2936조 4,015억 1,704만</t>
+    <t>2경 2936조 4015억 1704만</t>
   </si>
   <si>
     <t>프리프리</t>
@@ -2184,7 +2184,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
   </si>
   <si>
-    <t>2경 1323조 7,490억 7,475만</t>
+    <t>2경 1323조 7490억 7475만</t>
   </si>
   <si>
     <t>반가성</t>
@@ -2193,13 +2193,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EA%B0%80%EC%84%B1</t>
   </si>
   <si>
-    <t>1경 9258조 3,650억 1,564만</t>
+    <t>1경 9258조 3650억 1564만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
   </si>
   <si>
-    <t>1경 7139조 5,691억 7,924만</t>
+    <t>1경 7139조 5691억 7924만</t>
   </si>
   <si>
     <t>망겜감별사</t>
@@ -2208,7 +2208,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
   </si>
   <si>
-    <t>1경 5876조 1,968억 392만</t>
+    <t>1경 5876조 1968억 392만</t>
   </si>
   <si>
     <t>쌉새</t>
@@ -2217,7 +2217,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8C%89%EC%83%88</t>
   </si>
   <si>
-    <t>1경 5688조 4,374억 8,127만</t>
+    <t>1경 5688조 4374억 8127만</t>
   </si>
   <si>
     <t>루넨</t>
@@ -2226,7 +2226,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
   </si>
   <si>
-    <t>1경 3148조 5,412억 6,446만</t>
+    <t>1경 3148조 5412억 6446만</t>
   </si>
   <si>
     <t>니뚜</t>
@@ -2235,7 +2235,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%9A%9C</t>
   </si>
   <si>
-    <t>1경 2312조 9,961억 3,717만</t>
+    <t>1경 2819조 4851억 9770만</t>
   </si>
   <si>
     <t>라똥삐</t>
@@ -2244,7 +2244,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%98%A5%EC%82%90</t>
   </si>
   <si>
-    <t>1경 2085조 1,284억 3,396만</t>
+    <t>1경 2085조 1284억 3396만</t>
   </si>
   <si>
     <t>오곤</t>
@@ -2253,7 +2253,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EA%B3%A4</t>
   </si>
   <si>
-    <t>1경 1856조 4,618억 6,137만</t>
+    <t>1경 1856조 4618억 6137만</t>
   </si>
   <si>
     <t>제로슈가</t>
@@ -2262,7 +2262,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
   </si>
   <si>
-    <t>1경 2,945억 9,039만</t>
+    <t>1경 2945억 9039만</t>
   </si>
   <si>
     <t>러너</t>
@@ -2271,7 +2271,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9F%AC%EB%84%88</t>
   </si>
   <si>
-    <t>6443조 2,165억 2,470만</t>
+    <t>6443조 2165억 2470만</t>
   </si>
   <si>
     <t>해찬나래</t>
@@ -2280,7 +2280,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EC%B0%AC%EB%82%98%EB%9E%98</t>
   </si>
   <si>
-    <t>5796조 3,675억 8,873만</t>
+    <t>5796조 3675억 8873만</t>
   </si>
   <si>
     <t>갓겜감별사</t>
@@ -2292,7 +2292,7 @@
     <t>110</t>
   </si>
   <si>
-    <t>341조 6,408억 9,657만</t>
+    <t>341조 6408억 9657만</t>
   </si>
 </sst>
 </file>
@@ -3025,7 +3025,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="27.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4070,7 +4070,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="26.7109375" customWidth="1"/>
+    <col min="9" max="9" width="24.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5082,7 +5082,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="26.7109375" customWidth="1"/>
+    <col min="9" max="9" width="24.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6094,7 +6094,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="26.7109375" customWidth="1"/>
+    <col min="9" max="9" width="24.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7106,7 +7106,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="26.7109375" customWidth="1"/>
+    <col min="9" max="9" width="24.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8151,7 +8151,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="26.7109375" customWidth="1"/>
+    <col min="9" max="9" width="24.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9196,7 +9196,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9380,7 +9380,7 @@
         <v>87</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>125</v>
+        <v>94</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>154</v>
@@ -9412,7 +9412,7 @@
         <v>87</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>154</v>
@@ -9508,10 +9508,10 @@
         <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>177</v>
+        <v>105</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>159</v>
+        <v>191</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>696</v>
@@ -9540,10 +9540,10 @@
         <v>87</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>105</v>
+        <v>177</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>699</v>
